--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.44349561635992</v>
+        <v>7.709568037658487</v>
       </c>
       <c r="D2" t="n">
-        <v>47.30690044461009</v>
+        <v>7.68737132224914</v>
       </c>
       <c r="E2" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F2" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.52321094515158</v>
+        <v>6.097521778587131</v>
       </c>
       <c r="D3" t="n">
-        <v>37.43039095421349</v>
+        <v>6.082438530059692</v>
       </c>
       <c r="E3" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F3" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.04678153921662</v>
+        <v>3.2576020001227</v>
       </c>
       <c r="D4" t="n">
-        <v>20.88548470274601</v>
+        <v>3.393891264196226</v>
       </c>
       <c r="E4" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F4" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.52706640779236</v>
+        <v>4.635648291266258</v>
       </c>
       <c r="D5" t="n">
-        <v>29.32486561502556</v>
+        <v>4.765290662441654</v>
       </c>
       <c r="E5" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F5" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.91602091207939</v>
+        <v>3.561353398212901</v>
       </c>
       <c r="D6" t="n">
-        <v>21.45667354632842</v>
+        <v>3.486709451278369</v>
       </c>
       <c r="E6" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F6" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.53895652030477</v>
+        <v>6.100080434549525</v>
       </c>
       <c r="D7" t="n">
-        <v>37.01745473800279</v>
+        <v>6.015336394925454</v>
       </c>
       <c r="E7" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F7" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.697866812793</v>
+        <v>6.288403357078863</v>
       </c>
       <c r="D8" t="n">
-        <v>39.42631950564363</v>
+        <v>6.406776919667091</v>
       </c>
       <c r="E8" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F8" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.46054835792034</v>
+        <v>7.387339108162055</v>
       </c>
       <c r="D9" t="n">
-        <v>46.32658632874318</v>
+        <v>7.528070278420768</v>
       </c>
       <c r="E9" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F9" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.23038971782404</v>
+        <v>7.024938329146407</v>
       </c>
       <c r="D10" t="n">
-        <v>43.73553987664822</v>
+        <v>7.107025229955336</v>
       </c>
       <c r="E10" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F10" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>50.85219121399822</v>
+        <v>8.263481072274711</v>
       </c>
       <c r="D11" t="n">
-        <v>50.38923097995995</v>
+        <v>8.188250034243493</v>
       </c>
       <c r="E11" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F11" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.17630241832324</v>
+        <v>7.341149142977526</v>
       </c>
       <c r="D12" t="n">
-        <v>45.69074091178013</v>
+        <v>7.424745398164272</v>
       </c>
       <c r="E12" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F12" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.49775532900891</v>
+        <v>7.880885240963948</v>
       </c>
       <c r="D13" t="n">
-        <v>48.98237811397566</v>
+        <v>7.959636443521045</v>
       </c>
       <c r="E13" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F13" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.75279114496936</v>
+        <v>6.622328561057522</v>
       </c>
       <c r="D14" t="n">
-        <v>41.19649022245368</v>
+        <v>6.694429661148724</v>
       </c>
       <c r="E14" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F14" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>50.31520280222857</v>
+        <v>8.176220455362143</v>
       </c>
       <c r="D15" t="n">
-        <v>50.72881971778006</v>
+        <v>8.24343320413926</v>
       </c>
       <c r="E15" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F15" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>67.53562742236537</v>
+        <v>10.97453945613437</v>
       </c>
       <c r="D16" t="n">
-        <v>67.64458531865709</v>
+        <v>10.99224511428178</v>
       </c>
       <c r="E16" t="n">
-        <v>11.57995545839999</v>
+        <v>1.881742761989999</v>
       </c>
       <c r="F16" t="n">
-        <v>11.53998850082058</v>
+        <v>1.875248131383344</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
